--- a/data/trans_dic/P1427-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1427-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,31</t>
+          <t>0,43; 3,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,07</t>
+          <t>0,23; 2,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,07</t>
+          <t>1,68; 3,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,03</t>
+          <t>0,59; 3,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,1</t>
+          <t>1,11; 3,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,2</t>
+          <t>0,39; 2,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,56</t>
+          <t>0,61; 2,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,16</t>
+          <t>1,61; 3,1</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,96</t>
+          <t>0,51; 3,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,16</t>
+          <t>0,24; 2,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,61</t>
+          <t>1,18; 3,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,53</t>
+          <t>0,24; 2,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,71</t>
+          <t>1,32; 3,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,87</t>
+          <t>0,63; 2,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,73</t>
+          <t>0,37; 1,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,12</t>
+          <t>1,55; 3,14</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,78</t>
+          <t>1,32; 3,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,66</t>
+          <t>1,14; 3,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,36</t>
+          <t>1,73; 4,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,13</t>
+          <t>0,38; 3,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,95</t>
+          <t>0,67; 6,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,38</t>
+          <t>3,35; 8,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,21</t>
+          <t>1,25; 3,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,54</t>
+          <t>1,38; 3,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,09</t>
+          <t>2,5; 4,76</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,1</t>
+          <t>2,06; 4,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,34</t>
+          <t>0,31; 1,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 5,26</t>
+          <t>2,92; 4,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,78</t>
+          <t>0,86; 2,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,45</t>
+          <t>1,27; 3,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,27</t>
+          <t>2,17; 3,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,14</t>
+          <t>1,71; 3,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,82</t>
+          <t>0,85; 1,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,02</t>
+          <t>2,83; 4,23</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,85</t>
+          <t>0,62; 2,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,81</t>
+          <t>0,9; 2,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,36</t>
+          <t>3,31; 6,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,92</t>
+          <t>2,25; 4,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,4</t>
+          <t>1,76; 4,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 9,67</t>
+          <t>5,97; 8,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,6</t>
+          <t>1,76; 3,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,21</t>
+          <t>1,62; 3,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 7,78</t>
+          <t>5,11; 7,01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,57</t>
+          <t>0,2; 2,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,86</t>
+          <t>3,24; 5,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,69</t>
+          <t>1,59; 3,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,99</t>
+          <t>4,39; 6,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,62</t>
+          <t>2,61; 4,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,88</t>
+          <t>1,27; 2,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,57</t>
+          <t>3,57; 5,57</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,57</t>
+          <t>1,51; 2,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1348,37 +1348,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 3,67</t>
+          <t>2,63; 3,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,31</t>
+          <t>2,14; 3,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,84</t>
+          <t>1,76; 2,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,48; 4,95</t>
+          <t>3,9; 4,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,73</t>
+          <t>1,98; 2,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,98</t>
+          <t>1,38; 2,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,16</t>
+          <t>3,46; 4,15</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22029</t>
+          <t>23722</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1930; 14458</t>
+          <t>1889; 14478</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>973; 8887</t>
+          <t>973; 9869</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8961; 20585</t>
+          <t>9265; 20917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5590</t>
+          <t>0; 5414</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2078; 13971</t>
+          <t>2047; 13647</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4967; 13855</t>
+          <t>5411; 15028</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2848; 16571</t>
+          <t>2924; 15635</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4875; 19887</t>
+          <t>4723; 18542</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15468; 30134</t>
+          <t>16703; 32216</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>20373</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2396; 16567</t>
+          <t>2137; 15981</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>913; 8163</t>
+          <t>902; 8097</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5912; 16325</t>
+          <t>5721; 17008</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 12917</t>
+          <t>0; 10904</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>881; 9422</t>
+          <t>884; 8538</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4999; 14164</t>
+          <t>5595; 15756</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4301; 21729</t>
+          <t>4736; 21154</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2738; 12977</t>
+          <t>2758; 13023</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12697; 26042</t>
+          <t>14004; 28447</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21341</t>
+          <t>22569</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9066; 23807</t>
+          <t>8316; 24762</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5882; 19079</t>
+          <t>5955; 19543</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4058; 22463</t>
+          <t>8138; 18926</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>991; 8151</t>
+          <t>994; 8504</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1267; 11539</t>
+          <t>1106; 10368</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5644; 13952</t>
+          <t>6265; 15264</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11776; 28548</t>
+          <t>11113; 27975</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9352; 24378</t>
+          <t>9509; 24984</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7735; 34092</t>
+          <t>16467; 31334</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41335</t>
+          <t>43518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22589</t>
+          <t>24537</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>63924</t>
+          <t>68055</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23058; 47491</t>
+          <t>23849; 46795</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3745; 15361</t>
+          <t>3605; 14299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32072; 54271</t>
+          <t>32907; 55830</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6077; 21265</t>
+          <t>6603; 21594</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10326; 28457</t>
+          <t>10493; 28518</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10520; 31988</t>
+          <t>18652; 32289</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31783; 60320</t>
+          <t>32808; 61512</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15852; 35894</t>
+          <t>16878; 37340</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43824; 80758</t>
+          <t>56199; 84128</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24885</t>
+          <t>25589</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59503</t>
+          <t>58985</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>84388</t>
+          <t>84573</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3210; 14564</t>
+          <t>3175; 14873</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5297; 17463</t>
+          <t>5556; 17726</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18126; 34868</t>
+          <t>18763; 34867</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16331; 37377</t>
+          <t>17071; 36416</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13541; 32465</t>
+          <t>12976; 32475</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44016; 81119</t>
+          <t>49554; 69825</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21994; 45741</t>
+          <t>22349; 45257</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21297; 43586</t>
+          <t>22026; 43890</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>66445; 102099</t>
+          <t>71362; 97914</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42989</t>
+          <t>46392</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>44861</t>
+          <t>48229</t>
         </is>
       </c>
     </row>
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>470; 6174</t>
+          <t>464; 5500</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35419; 65015</t>
+          <t>35946; 64205</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18473; 39947</t>
+          <t>17200; 39607</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34502; 53127</t>
+          <t>36976; 58056</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35639; 63547</t>
+          <t>35917; 63954</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17943; 39469</t>
+          <t>17429; 40303</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>36467; 55698</t>
+          <t>38599; 60190</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103704</t>
+          <t>107741</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>151445</t>
+          <t>159780</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>255150</t>
+          <t>267521</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>53210; 87972</t>
+          <t>51514; 87568</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25493; 47712</t>
+          <t>25374; 47765</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79711; 123747</t>
+          <t>90464; 125735</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76297; 117487</t>
+          <t>75968; 113931</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>64130; 100427</t>
+          <t>62134; 101214</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>124455; 176797</t>
+          <t>141720; 178593</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>137445; 190168</t>
+          <t>137981; 190642</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>95789; 136995</t>
+          <t>95611; 140724</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>218719; 288766</t>
+          <t>244932; 293290</t>
         </is>
       </c>
     </row>
